--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2109,6 +2109,785 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130232738</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lördag, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>504067</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6691556</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130232740</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lördag, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>504089</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6691612</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130232735</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lördag, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>504104</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6691565</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130233499</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>503920</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6691611</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130233568</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92923</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>504129</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6691806</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130226891</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bunkfallet, Bunkfallet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>503886</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6691630</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130233531</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>504000</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6691844</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2111,7 +2111,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130232738</v>
+        <v>130233499</v>
       </c>
       <c r="B12" t="n">
         <v>79095</v>
@@ -2140,16 +2140,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lördag, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504067</v>
+        <v>503920</v>
       </c>
       <c r="R12" t="n">
-        <v>6691556</v>
+        <v>6691611</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2181,7 +2184,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2191,7 +2194,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2200,25 +2203,26 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130232740</v>
+        <v>130232738</v>
       </c>
       <c r="B13" t="n">
         <v>79095</v>
@@ -2253,10 +2257,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504089</v>
+        <v>504067</v>
       </c>
       <c r="R13" t="n">
-        <v>6691612</v>
+        <v>6691556</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2288,7 +2292,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2298,7 +2302,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2325,7 +2329,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130232735</v>
+        <v>130232740</v>
       </c>
       <c r="B14" t="n">
         <v>79095</v>
@@ -2360,10 +2364,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504104</v>
+        <v>504089</v>
       </c>
       <c r="R14" t="n">
-        <v>6691565</v>
+        <v>6691612</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2395,7 +2399,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2405,7 +2409,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2432,7 +2436,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130233499</v>
+        <v>130232735</v>
       </c>
       <c r="B15" t="n">
         <v>79095</v>
@@ -2461,19 +2465,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Lördag, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503920</v>
+        <v>504104</v>
       </c>
       <c r="R15" t="n">
-        <v>6691611</v>
+        <v>6691565</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2505,7 +2506,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2515,7 +2516,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2524,19 +2525,18 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2114,7 +2114,7 @@
         <v>130233499</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>130232738</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>130232740</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>130232735</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130233568</v>
       </c>
       <c r="B16" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>130226891</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>130233531</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,6 +2888,520 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130255252</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LÅngmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>504096</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6691514</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130255228</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fäbromyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>503987</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6691819</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosökshack i äldre gran.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130255257</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långmyran., Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>504080</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6691318</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130255235</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fäbromyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>503994</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6691810</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130255260</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>503978</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6691268</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2111,7 +2111,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130233499</v>
+        <v>130232738</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -2140,19 +2140,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Lördag, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503920</v>
+        <v>504067</v>
       </c>
       <c r="R12" t="n">
-        <v>6691611</v>
+        <v>6691556</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2184,7 +2181,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2194,7 +2191,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2203,26 +2200,25 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130232738</v>
+        <v>130232740</v>
       </c>
       <c r="B13" t="n">
         <v>79180</v>
@@ -2257,10 +2253,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504067</v>
+        <v>504089</v>
       </c>
       <c r="R13" t="n">
-        <v>6691556</v>
+        <v>6691612</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2292,7 +2288,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2302,7 +2298,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2329,7 +2325,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130232740</v>
+        <v>130232735</v>
       </c>
       <c r="B14" t="n">
         <v>79180</v>
@@ -2364,10 +2360,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504089</v>
+        <v>504104</v>
       </c>
       <c r="R14" t="n">
-        <v>6691612</v>
+        <v>6691565</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2399,7 +2395,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2409,7 +2405,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2436,7 +2432,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130232735</v>
+        <v>130233499</v>
       </c>
       <c r="B15" t="n">
         <v>79180</v>
@@ -2465,16 +2461,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lördag, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504104</v>
+        <v>503920</v>
       </c>
       <c r="R15" t="n">
-        <v>6691565</v>
+        <v>6691611</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2506,7 +2505,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2516,7 +2515,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2525,18 +2524,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2111,7 +2111,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130232738</v>
+        <v>130233499</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -2140,16 +2140,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lördag, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504067</v>
+        <v>503920</v>
       </c>
       <c r="R12" t="n">
-        <v>6691556</v>
+        <v>6691611</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2181,7 +2184,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2191,7 +2194,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2200,25 +2203,26 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130232740</v>
+        <v>130232738</v>
       </c>
       <c r="B13" t="n">
         <v>79180</v>
@@ -2253,10 +2257,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504089</v>
+        <v>504067</v>
       </c>
       <c r="R13" t="n">
-        <v>6691612</v>
+        <v>6691556</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2288,7 +2292,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2298,7 +2302,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2325,7 +2329,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130232735</v>
+        <v>130232740</v>
       </c>
       <c r="B14" t="n">
         <v>79180</v>
@@ -2360,10 +2364,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504104</v>
+        <v>504089</v>
       </c>
       <c r="R14" t="n">
-        <v>6691565</v>
+        <v>6691612</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2395,7 +2399,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2405,7 +2409,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2432,7 +2436,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130233499</v>
+        <v>130232735</v>
       </c>
       <c r="B15" t="n">
         <v>79180</v>
@@ -2461,19 +2465,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Lördag, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503920</v>
+        <v>504104</v>
       </c>
       <c r="R15" t="n">
-        <v>6691611</v>
+        <v>6691565</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2505,7 +2506,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2515,7 +2516,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2524,19 +2525,18 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2114,7 +2114,7 @@
         <v>130233499</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>130232738</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>130232740</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>130232735</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130233568</v>
       </c>
       <c r="B16" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>130233531</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>130255252</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>130255257</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>130255235</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>130255260</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2114,7 +2114,7 @@
         <v>130233499</v>
       </c>
       <c r="B12" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>130232738</v>
       </c>
       <c r="B13" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>130232740</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>130232735</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130233568</v>
       </c>
       <c r="B16" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>130226891</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>130233531</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>130255252</v>
       </c>
       <c r="B19" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>130255228</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>130255257</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>130255235</v>
       </c>
       <c r="B22" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>130255260</v>
       </c>
       <c r="B23" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2546,7 +2546,7 @@
         <v>130233568</v>
       </c>
       <c r="B16" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2546,7 +2546,7 @@
         <v>130233568</v>
       </c>
       <c r="B16" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2114,7 +2114,7 @@
         <v>130233499</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>130232738</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>130232740</v>
       </c>
       <c r="B14" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>130232735</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130233568</v>
       </c>
       <c r="B16" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>130226891</v>
       </c>
       <c r="B17" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>130233531</v>
       </c>
       <c r="B18" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>130255252</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>130255228</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>130255257</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>130255235</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>130255260</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2546,7 +2546,7 @@
         <v>130233568</v>
       </c>
       <c r="B16" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -2893,7 +2893,7 @@
         <v>130255252</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>130255228</v>
       </c>
       <c r="B20" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>130255257</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>130255235</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>130255260</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49783-2024 artfynd.xlsx
+++ b/artfynd/A 49783-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>16846185</v>
       </c>
       <c r="B2" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503854.7947895175</v>
+        <v>503855</v>
       </c>
       <c r="R2" t="n">
-        <v>6691829.414286981</v>
+        <v>6691829</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,19 +745,9 @@
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-11-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -820,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16846199</v>
+        <v>16846190</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,31 +816,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -870,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503878.9548253385</v>
+        <v>503828</v>
       </c>
       <c r="R3" t="n">
-        <v>6691479.637272649</v>
+        <v>6691837</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,27 +883,18 @@
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -967,15 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16846193</v>
+        <v>130233568</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,21 +949,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,20 +973,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyran - Storolles - Anders-Ers, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503949.329181792</v>
+        <v>504129</v>
       </c>
       <c r="R4" t="n">
-        <v>6691481.692186418</v>
+        <v>6691806</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1047,22 +1014,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-11-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-11-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,90 +1038,61 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Anders Janols</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16846190</v>
+        <v>16846191</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1164,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503828.0261338673</v>
+        <v>503930</v>
       </c>
       <c r="R5" t="n">
-        <v>6691837.301948918</v>
+        <v>6691592</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1197,28 +1135,17 @@
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1242,9 +1169,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1262,19 +1194,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16846200</v>
+        <v>16846193</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1297,7 +1224,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1312,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503823.7377571082</v>
+        <v>503949</v>
       </c>
       <c r="R6" t="n">
-        <v>6691674.02772129</v>
+        <v>6691482</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1345,19 +1272,9 @@
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-11-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1409,19 +1326,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16846191</v>
+        <v>16846195</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1459,10 +1371,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503929.8817406236</v>
+        <v>503975</v>
       </c>
       <c r="R7" t="n">
-        <v>6691591.513714024</v>
+        <v>6691461</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1492,21 +1404,11 @@
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1536,14 +1438,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1561,19 +1458,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16846195</v>
+        <v>16846196</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1596,7 +1488,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1611,10 +1503,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503975.1235590717</v>
+        <v>503982</v>
       </c>
       <c r="R8" t="n">
-        <v>6691460.938884141</v>
+        <v>6691466</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1644,21 +1536,11 @@
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1688,9 +1570,12 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AN8" t="n">
+        <v>4</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>4 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1711,16 +1596,11 @@
         <v>16846197</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1758,10 +1638,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504049.9223644526</v>
+        <v>504050</v>
       </c>
       <c r="R9" t="n">
-        <v>6691495.657013932</v>
+        <v>6691496</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1791,19 +1671,9 @@
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-11-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1855,19 +1725,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16846196</v>
+        <v>16846199</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1890,7 +1755,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1905,10 +1770,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503982.0567061641</v>
+        <v>503879</v>
       </c>
       <c r="R10" t="n">
-        <v>6691465.894432432</v>
+        <v>6691480</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1938,21 +1803,11 @@
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2014-11-17</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1982,12 +1837,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AN10" t="n">
-        <v>4</v>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>4 substratenheter # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2005,56 +1857,58 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117573563</v>
+        <v>16846200</v>
       </c>
       <c r="B11" t="n">
-        <v>77418</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6000248</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Anders-Ers, Dlr</t>
+          <t>Långmyran - Storolles - Anders-Ers, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504104</v>
+        <v>503824</v>
       </c>
       <c r="R11" t="n">
-        <v>6691433</v>
+        <v>6691674</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2078,12 +1932,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2014-11-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2014-11-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2092,33 +1946,57 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Öster, Niklas Trogen</t>
+          <t>Janolof Hermansson, Anders Janols</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130233499</v>
+        <v>16846203</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2139,20 +2017,27 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Långmyran - Storolles - Anders-Ers, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503920</v>
+        <v>503797</v>
       </c>
       <c r="R12" t="n">
-        <v>6691611</v>
+        <v>6691778</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2179,22 +2064,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2014-11-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2014-11-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2203,33 +2078,57 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Janolof Hermansson, Anders Janols</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130232738</v>
+        <v>130232721</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2257,10 +2156,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504067</v>
+        <v>504099</v>
       </c>
       <c r="R13" t="n">
-        <v>6691556</v>
+        <v>6691758</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2292,7 +2191,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2302,7 +2201,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2329,14 +2228,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130232740</v>
+        <v>130232722</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2364,10 +2263,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504089</v>
+        <v>504160</v>
       </c>
       <c r="R14" t="n">
-        <v>6691612</v>
+        <v>6691770</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2399,7 +2298,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2409,7 +2308,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2439,11 +2338,11 @@
         <v>130232735</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2543,56 +2442,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130233568</v>
+        <v>130232737</v>
       </c>
       <c r="B16" t="n">
-        <v>93047</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Lördag, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504129</v>
+        <v>504067</v>
       </c>
       <c r="R16" t="n">
-        <v>6691806</v>
+        <v>6691556</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2624,7 +2512,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2634,7 +2522,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2643,69 +2531,63 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130226891</v>
+        <v>130232739</v>
       </c>
       <c r="B17" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bunkfallet, Bunkfallet, Dlr</t>
+          <t>Lördag, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503886</v>
+        <v>504089</v>
       </c>
       <c r="R17" t="n">
-        <v>6691630</v>
+        <v>6691612</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2737,7 +2619,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2747,12 +2629,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2779,14 +2656,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130233531</v>
+        <v>130233499</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2817,10 +2694,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504000</v>
+        <v>503920</v>
       </c>
       <c r="R18" t="n">
-        <v>6691844</v>
+        <v>6691611</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2852,7 +2729,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2862,7 +2739,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2890,14 +2767,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130255252</v>
+        <v>130233531</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2924,17 +2801,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>LÅngmyran, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504096</v>
+        <v>504000</v>
       </c>
       <c r="R19" t="n">
-        <v>6691514</v>
+        <v>6691844</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2961,9 +2838,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2979,54 +2866,49 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130255228</v>
+        <v>130255235</v>
       </c>
       <c r="B20" t="n">
-        <v>57859</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3034,10 +2916,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503987</v>
+        <v>503994</v>
       </c>
       <c r="R20" t="n">
-        <v>6691819</v>
+        <v>6691810</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3064,17 +2946,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack i äldre gran.</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3083,6 +2960,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3101,14 +2979,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130255257</v>
+        <v>130255246</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3135,14 +3013,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långmyran., Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504080</v>
+        <v>504141</v>
       </c>
       <c r="R21" t="n">
-        <v>6691318</v>
+        <v>6691611</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3202,14 +3080,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130255235</v>
+        <v>130255252</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3236,14 +3114,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fäbromyran, Dlr</t>
+          <t>LÅngmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503994</v>
+        <v>504096</v>
       </c>
       <c r="R22" t="n">
-        <v>6691810</v>
+        <v>6691514</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3303,14 +3181,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130255260</v>
+        <v>130255257</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3337,14 +3215,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Långmyran., Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503978</v>
+        <v>504080</v>
       </c>
       <c r="R23" t="n">
-        <v>6691268</v>
+        <v>6691318</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3401,6 +3279,676 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130255260</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>503978</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6691268</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130232733</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lördag, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>504160</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6691770</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130255228</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fäbromyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>503987</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6691819</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökshack i äldre gran.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130226891</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bunkfallet, Bunkfallet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>503886</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6691630</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131078252</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>504140</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6691587</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Jag lockar fram tuppen med järppipa efter att ha stött den under skidåkning.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>117573563</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78338</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Anders-Ers, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>504104</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6691433</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
